--- a/data/trans_orig/P36B10-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P36B10-Habitat-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia de consumo de embutidos y fiambres en 2007</t>
+          <t>Población según la frecuencia de consumo de embutidos y fiambres en 2007 (tasa de respuesta: 99,74%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9358</t>
+          <t>9805</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>27007</t>
+          <t>27133</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>22848</t>
+          <t>22257</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>45335</t>
+          <t>45714</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>37394</t>
+          <t>36933</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>66956</t>
+          <t>63696</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,61%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>45883</t>
+          <t>46362</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>74002</t>
+          <t>75676</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>10,9%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>75899</t>
+          <t>76462</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>110959</t>
+          <t>111252</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>16,16%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>130241</t>
+          <t>130499</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>176441</t>
+          <t>173711</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>12,57%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>165611</t>
+          <t>163285</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>211005</t>
+          <t>209733</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>23,86%</t>
+          <t>23,53%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>30,4%</t>
+          <t>30,22%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>252963</t>
+          <t>250085</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>303706</t>
+          <t>300776</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>36,75%</t>
+          <t>36,33%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>44,12%</t>
+          <t>43,7%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>427147</t>
+          <t>431801</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>496597</t>
+          <t>499987</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>30,9%</t>
+          <t>31,24%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>35,92%</t>
+          <t>36,17%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>183933</t>
+          <t>182066</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>231297</t>
+          <t>231474</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>26,5%</t>
+          <t>26,23%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>33,33%</t>
+          <t>33,35%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>175077</t>
+          <t>173731</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>220582</t>
+          <t>221112</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>25,43%</t>
+          <t>25,24%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>32,05%</t>
+          <t>32,12%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>366851</t>
+          <t>370804</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>435650</t>
+          <t>438872</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>26,54%</t>
+          <t>26,82%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>31,51%</t>
+          <t>31,75%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>201476</t>
+          <t>202779</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>249914</t>
+          <t>250599</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>29,03%</t>
+          <t>29,22%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>36,01%</t>
+          <t>36,11%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>74185</t>
+          <t>74153</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>107230</t>
+          <t>109217</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>15,87%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>286119</t>
+          <t>287924</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>349445</t>
+          <t>346540</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>20,7%</t>
+          <t>20,83%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>25,28%</t>
+          <t>25,07%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>43673</t>
+          <t>45052</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>74955</t>
+          <t>76028</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>62523</t>
+          <t>64225</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>96475</t>
+          <t>98010</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>115003</t>
+          <t>113953</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>163742</t>
+          <t>161649</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>8,41%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>81924</t>
+          <t>80472</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>118919</t>
+          <t>120607</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>12,59%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>130156</t>
+          <t>128606</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>176018</t>
+          <t>176758</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>13,33%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>18,25%</t>
+          <t>18,32%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>220716</t>
+          <t>225366</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>282418</t>
+          <t>288248</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>14,69%</t>
+          <t>14,99%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>272555</t>
+          <t>273518</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>327148</t>
+          <t>332614</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>28,46%</t>
+          <t>28,56%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>34,16%</t>
+          <t>34,73%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>405718</t>
+          <t>407791</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>466592</t>
+          <t>471322</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>42,06%</t>
+          <t>42,27%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>48,37%</t>
+          <t>48,86%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>693464</t>
+          <t>691944</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>777997</t>
+          <t>778978</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>36,07%</t>
+          <t>35,99%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>40,47%</t>
+          <t>40,52%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>279181</t>
+          <t>278468</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>339387</t>
+          <t>337647</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>29,15%</t>
+          <t>29,08%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>35,44%</t>
+          <t>35,26%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>203432</t>
+          <t>204595</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>258546</t>
+          <t>257779</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>21,09%</t>
+          <t>21,21%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>26,8%</t>
+          <t>26,72%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>498800</t>
+          <t>500329</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>578595</t>
+          <t>577903</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>25,95%</t>
+          <t>26,03%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>30,1%</t>
+          <t>30,06%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>169162</t>
+          <t>166183</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>218054</t>
+          <t>217141</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>17,35%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>22,77%</t>
+          <t>22,67%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>54716</t>
+          <t>53914</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>86955</t>
+          <t>85912</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>232809</t>
+          <t>233013</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>294676</t>
+          <t>290825</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>12,12%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>15,13%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>39037</t>
+          <t>37528</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>67930</t>
+          <t>67730</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>10,01%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>77873</t>
+          <t>77884</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>112801</t>
+          <t>114758</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,7 +2151,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>16,83%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>124550</t>
+          <t>121536</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>169968</t>
+          <t>169583</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,51%</t>
+          <t>12,48%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>94969</t>
+          <t>96836</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>136240</t>
+          <t>134666</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>14,31%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>20,13%</t>
+          <t>19,9%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>134174</t>
+          <t>133028</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>175860</t>
+          <t>176590</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>19,68%</t>
+          <t>19,51%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>25,8%</t>
+          <t>25,9%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>240461</t>
+          <t>240885</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>301142</t>
+          <t>298298</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>17,7%</t>
+          <t>17,73%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>22,17%</t>
+          <t>21,96%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>178829</t>
+          <t>180572</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>227684</t>
+          <t>227334</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>26,68%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>33,64%</t>
+          <t>33,59%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>227075</t>
+          <t>227420</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>275119</t>
+          <t>277470</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>33,31%</t>
+          <t>33,36%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>40,36%</t>
+          <t>40,7%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>418147</t>
+          <t>418109</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>486277</t>
+          <t>487637</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,7 +2412,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>35,79%</t>
+          <t>35,89%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>190989</t>
+          <t>191660</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>242512</t>
+          <t>243074</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>28,22%</t>
+          <t>28,32%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>35,83%</t>
+          <t>35,92%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>123977</t>
+          <t>121434</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>165594</t>
+          <t>164911</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18,19%</t>
+          <t>17,81%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>24,29%</t>
+          <t>24,19%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>324985</t>
+          <t>330081</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>389787</t>
+          <t>395548</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>23,92%</t>
+          <t>24,3%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>28,69%</t>
+          <t>29,12%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>71875</t>
+          <t>75251</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>111266</t>
+          <t>110195</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>11,12%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>16,44%</t>
+          <t>16,28%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>26766</t>
+          <t>28220</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>51085</t>
+          <t>51886</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>110066</t>
+          <t>110796</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>153192</t>
+          <t>153059</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>11,27%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>33108</t>
+          <t>33668</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>60719</t>
+          <t>59591</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>55587</t>
+          <t>56000</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>89310</t>
+          <t>89276</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,7 +2828,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>95891</t>
+          <t>96874</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>138386</t>
+          <t>139170</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>7,05%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>89567</t>
+          <t>92355</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>128928</t>
+          <t>130731</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>13,9%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>154226</t>
+          <t>152877</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>203521</t>
+          <t>199796</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>14,78%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>19,67%</t>
+          <t>19,31%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>255894</t>
+          <t>254217</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>316789</t>
+          <t>316697</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>12,87%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>305715</t>
+          <t>306875</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>362820</t>
+          <t>363227</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>32,51%</t>
+          <t>32,63%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>38,58%</t>
+          <t>38,62%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>390144</t>
+          <t>392447</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>453092</t>
+          <t>456344</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>37,71%</t>
+          <t>37,93%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>43,8%</t>
+          <t>44,11%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>716965</t>
+          <t>715458</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>803076</t>
+          <t>798943</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>36,3%</t>
+          <t>36,23%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>40,66%</t>
+          <t>40,45%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>243549</t>
+          <t>241894</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>296082</t>
+          <t>298080</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>25,9%</t>
+          <t>25,72%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>31,48%</t>
+          <t>31,69%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>213813</t>
+          <t>212854</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>267347</t>
+          <t>266374</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>20,67%</t>
+          <t>20,57%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>25,84%</t>
+          <t>25,75%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>471364</t>
+          <t>471884</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>548928</t>
+          <t>554130</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>23,87%</t>
+          <t>23,89%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>27,79%</t>
+          <t>28,06%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>157129</t>
+          <t>158836</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>208411</t>
+          <t>205708</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>16,71%</t>
+          <t>16,89%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>22,16%</t>
+          <t>21,87%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>104374</t>
+          <t>106425</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>145396</t>
+          <t>147982</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>10,29%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>14,05%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>278085</t>
+          <t>274613</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>339492</t>
+          <t>341763</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>13,9%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>17,19%</t>
+          <t>17,3%</t>
         </is>
       </c>
     </row>
@@ -3460,12 +3460,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>147149</t>
+          <t>146854</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>200076</t>
+          <t>201403</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3475,12 +3475,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>244383</t>
+          <t>244787</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>312451</t>
+          <t>311349</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>405475</t>
+          <t>411102</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>489687</t>
+          <t>490867</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,39%</t>
         </is>
       </c>
     </row>
@@ -3573,12 +3573,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>348060</t>
+          <t>348305</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>420463</t>
+          <t>421152</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3593,7 +3593,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>12,88%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>531170</t>
+          <t>534591</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>616837</t>
+          <t>618567</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>15,87%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>18,31%</t>
+          <t>18,36%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3643,12 +3643,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>902598</t>
+          <t>898898</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1020596</t>
+          <t>1015347</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>13,54%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>15,37%</t>
+          <t>15,3%</t>
         </is>
       </c>
     </row>
@@ -3686,12 +3686,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>970170</t>
+          <t>974825</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>1076535</t>
+          <t>1079092</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3701,12 +3701,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>29,68%</t>
+          <t>29,82%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>32,93%</t>
+          <t>33,01%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3721,12 +3721,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1328606</t>
+          <t>1329416</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>1442506</t>
+          <t>1445801</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>39,43%</t>
+          <t>39,46%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>42,81%</t>
+          <t>42,91%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3756,12 +3756,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>2335280</t>
+          <t>2338408</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>2486404</t>
+          <t>2493953</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>35,18%</t>
+          <t>35,23%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>37,46%</t>
+          <t>37,57%</t>
         </is>
       </c>
     </row>
@@ -3799,12 +3799,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>955487</t>
+          <t>946254</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>1055005</t>
+          <t>1051415</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3814,12 +3814,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>29,23%</t>
+          <t>28,95%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>32,27%</t>
+          <t>32,16%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3834,12 +3834,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>759735</t>
+          <t>760839</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>857937</t>
+          <t>857056</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>22,55%</t>
+          <t>22,58%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>25,46%</t>
+          <t>25,44%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3869,12 +3869,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>1731404</t>
+          <t>1731085</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>1877420</t>
+          <t>1879996</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3889,7 +3889,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>28,28%</t>
+          <t>28,32%</t>
         </is>
       </c>
     </row>
@@ -3912,12 +3912,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>644436</t>
+          <t>644680</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>736558</t>
+          <t>735910</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3927,12 +3927,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>19,71%</t>
+          <t>19,72%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>22,53%</t>
+          <t>22,51%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3947,12 +3947,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>289430</t>
+          <t>290864</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>353938</t>
+          <t>358949</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3982,12 +3982,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>962791</t>
+          <t>959103</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1074178</t>
+          <t>1067055</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>14,45%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>16,18%</t>
+          <t>16,07%</t>
         </is>
       </c>
     </row>
@@ -4179,7 +4179,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia de consumo de embutidos y fiambres en 2012</t>
+          <t>Población según la frecuencia de consumo de embutidos y fiambres en 2012 (tasa de respuesta: 99,43%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4374,12 +4374,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>29216</t>
+          <t>30556</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>55017</t>
+          <t>55968</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4389,12 +4389,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4409,12 +4409,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>57597</t>
+          <t>56163</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>90711</t>
+          <t>90495</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4424,12 +4424,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>13,13%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>94148</t>
+          <t>96923</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>137083</t>
+          <t>138695</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4459,12 +4459,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>9,98%</t>
         </is>
       </c>
     </row>
@@ -4487,12 +4487,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>129064</t>
+          <t>130761</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>174628</t>
+          <t>177599</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4502,12 +4502,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>18,42%</t>
+          <t>18,66%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>24,93%</t>
+          <t>25,35%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4522,12 +4522,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>152734</t>
+          <t>152386</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>197890</t>
+          <t>198075</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4537,12 +4537,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>22,17%</t>
+          <t>22,12%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>28,72%</t>
+          <t>28,75%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4557,12 +4557,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>295449</t>
+          <t>295994</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>358015</t>
+          <t>356735</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4572,12 +4572,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>21,26%</t>
+          <t>21,3%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>25,76%</t>
+          <t>25,67%</t>
         </is>
       </c>
     </row>
@@ -4600,12 +4600,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>193323</t>
+          <t>193179</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>247231</t>
+          <t>244791</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4615,12 +4615,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>27,59%</t>
+          <t>27,57%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>35,29%</t>
+          <t>34,94%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4635,12 +4635,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>237077</t>
+          <t>238746</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>287897</t>
+          <t>290996</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>34,41%</t>
+          <t>34,65%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>41,78%</t>
+          <t>42,23%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4670,12 +4670,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>446401</t>
+          <t>448189</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>516483</t>
+          <t>523714</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>32,12%</t>
+          <t>32,25%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>37,17%</t>
+          <t>37,69%</t>
         </is>
       </c>
     </row>
@@ -4713,12 +4713,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>179476</t>
+          <t>175599</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>228223</t>
+          <t>225041</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4728,12 +4728,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>25,62%</t>
+          <t>25,06%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>32,58%</t>
+          <t>32,12%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>114826</t>
+          <t>116145</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>156178</t>
+          <t>158806</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16,67%</t>
+          <t>16,86%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>22,67%</t>
+          <t>23,05%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>304535</t>
+          <t>303191</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>373579</t>
+          <t>369120</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>21,92%</t>
+          <t>21,82%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>26,88%</t>
+          <t>26,56%</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>72110</t>
+          <t>72241</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>107006</t>
+          <t>108863</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>15,27%</t>
+          <t>15,54%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4861,12 +4861,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>31717</t>
+          <t>32954</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>58895</t>
+          <t>59079</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4896,12 +4896,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>112972</t>
+          <t>112296</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>156615</t>
+          <t>153874</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>11,07%</t>
         </is>
       </c>
     </row>
@@ -5056,12 +5056,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>57213</t>
+          <t>56688</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>92681</t>
+          <t>92276</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5071,12 +5071,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5091,12 +5091,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>79370</t>
+          <t>78593</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>119894</t>
+          <t>116776</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>11,37%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5126,12 +5126,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>144290</t>
+          <t>146827</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>195807</t>
+          <t>197622</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>9,69%</t>
         </is>
       </c>
     </row>
@@ -5169,12 +5169,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>171807</t>
+          <t>170026</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>223034</t>
+          <t>221271</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5184,12 +5184,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>16,96%</t>
+          <t>16,79%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>22,02%</t>
+          <t>21,85%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5204,12 +5204,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>251742</t>
+          <t>249705</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>312870</t>
+          <t>309567</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>24,52%</t>
+          <t>24,32%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>30,47%</t>
+          <t>30,15%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5239,12 +5239,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>438856</t>
+          <t>437770</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>515063</t>
+          <t>517017</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>21,52%</t>
+          <t>21,46%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>25,25%</t>
+          <t>25,35%</t>
         </is>
       </c>
     </row>
@@ -5282,12 +5282,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>260592</t>
+          <t>263651</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>322717</t>
+          <t>322386</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>25,73%</t>
+          <t>26,03%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>31,87%</t>
+          <t>31,83%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5317,12 +5317,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>289724</t>
+          <t>290769</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>352532</t>
+          <t>352772</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>28,22%</t>
+          <t>28,32%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>34,33%</t>
+          <t>34,36%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>569206</t>
+          <t>574305</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>652675</t>
+          <t>654628</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>27,91%</t>
+          <t>28,16%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>32,0%</t>
+          <t>32,1%</t>
         </is>
       </c>
     </row>
@@ -5395,12 +5395,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>282620</t>
+          <t>286516</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>345176</t>
+          <t>347336</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5410,12 +5410,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>27,91%</t>
+          <t>28,29%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>34,08%</t>
+          <t>34,3%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5430,12 +5430,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>204570</t>
+          <t>204912</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>263481</t>
+          <t>261861</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5445,12 +5445,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19,92%</t>
+          <t>19,96%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>25,66%</t>
+          <t>25,5%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5465,12 +5465,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>504701</t>
+          <t>505909</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>584336</t>
+          <t>587452</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>24,75%</t>
+          <t>24,8%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>28,65%</t>
+          <t>28,8%</t>
         </is>
       </c>
     </row>
@@ -5508,12 +5508,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>117590</t>
+          <t>119207</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>163276</t>
+          <t>164020</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5523,12 +5523,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>11,77%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>16,2%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>77903</t>
+          <t>79262</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>115662</t>
+          <t>116418</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5558,12 +5558,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>11,34%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>206539</t>
+          <t>207369</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>266629</t>
+          <t>265092</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5593,12 +5593,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>13,07%</t>
+          <t>13,0%</t>
         </is>
       </c>
     </row>
@@ -5738,12 +5738,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>43791</t>
+          <t>43382</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>73996</t>
+          <t>74814</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5753,12 +5753,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5773,12 +5773,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>67600</t>
+          <t>67851</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>104873</t>
+          <t>104413</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>13,49%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5808,12 +5808,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>121100</t>
+          <t>120000</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>167477</t>
+          <t>167733</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>10,98%</t>
         </is>
       </c>
     </row>
@@ -5851,12 +5851,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>119238</t>
+          <t>116367</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>165596</t>
+          <t>163571</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5866,12 +5866,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>15,45%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>21,98%</t>
+          <t>21,71%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5886,12 +5886,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>157998</t>
+          <t>160105</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>207574</t>
+          <t>209043</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5901,12 +5901,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>20,42%</t>
+          <t>20,69%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>26,82%</t>
+          <t>27,01%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5921,12 +5921,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>290028</t>
+          <t>289741</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>358173</t>
+          <t>361988</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5936,12 +5936,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>18,99%</t>
+          <t>18,97%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>23,45%</t>
+          <t>23,7%</t>
         </is>
       </c>
     </row>
@@ -5964,12 +5964,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>185140</t>
+          <t>186264</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>235915</t>
+          <t>238705</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5979,12 +5979,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>24,58%</t>
+          <t>24,73%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>31,32%</t>
+          <t>31,69%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>218580</t>
+          <t>220661</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>274711</t>
+          <t>275188</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>28,24%</t>
+          <t>28,51%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>35,5%</t>
+          <t>35,56%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>421894</t>
+          <t>419683</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>497296</t>
+          <t>494946</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>27,62%</t>
+          <t>27,48%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>32,56%</t>
+          <t>32,41%</t>
         </is>
       </c>
     </row>
@@ -6077,12 +6077,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>169440</t>
+          <t>167815</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>220272</t>
+          <t>216058</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6092,12 +6092,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>22,49%</t>
+          <t>22,28%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>29,24%</t>
+          <t>28,68%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>132767</t>
+          <t>132105</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>178513</t>
+          <t>178451</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>17,16%</t>
+          <t>17,07%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>23,07%</t>
+          <t>23,06%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>313748</t>
+          <t>314083</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>382827</t>
+          <t>381345</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>20,54%</t>
+          <t>20,57%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>25,07%</t>
+          <t>24,97%</t>
         </is>
       </c>
     </row>
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>130672</t>
+          <t>129206</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>176544</t>
+          <t>179364</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6205,12 +6205,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>17,35%</t>
+          <t>17,15%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>23,44%</t>
+          <t>23,81%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>87419</t>
+          <t>87858</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>127957</t>
+          <t>128475</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6240,12 +6240,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>16,53%</t>
+          <t>16,6%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>227715</t>
+          <t>226822</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>288974</t>
+          <t>288211</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6275,12 +6275,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>14,85%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>18,92%</t>
+          <t>18,87%</t>
         </is>
       </c>
     </row>
@@ -6420,12 +6420,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>52132</t>
+          <t>54232</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>84702</t>
+          <t>85529</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6435,12 +6435,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6455,12 +6455,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>120504</t>
+          <t>120689</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>165160</t>
+          <t>166935</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6470,12 +6470,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>15,81%</t>
+          <t>15,98%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6490,12 +6490,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>184568</t>
+          <t>184804</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>241225</t>
+          <t>242046</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6505,12 +6505,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>12,19%</t>
         </is>
       </c>
     </row>
@@ -6533,12 +6533,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>185452</t>
+          <t>185353</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>239588</t>
+          <t>239662</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6548,12 +6548,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>19,7%</t>
+          <t>19,69%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>25,45%</t>
+          <t>25,46%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6568,12 +6568,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>293599</t>
+          <t>297334</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>355227</t>
+          <t>358575</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>28,1%</t>
+          <t>28,46%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>34,0%</t>
+          <t>34,32%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6603,12 +6603,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>493303</t>
+          <t>495601</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>576703</t>
+          <t>577962</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6618,12 +6618,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>24,84%</t>
+          <t>24,95%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>29,04%</t>
+          <t>29,1%</t>
         </is>
       </c>
     </row>
@@ -6646,12 +6646,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>285157</t>
+          <t>285282</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>347162</t>
+          <t>346594</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6661,12 +6661,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>30,29%</t>
+          <t>30,3%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>36,88%</t>
+          <t>36,82%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6681,12 +6681,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>275305</t>
+          <t>272818</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>335511</t>
+          <t>333387</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6696,12 +6696,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>26,35%</t>
+          <t>26,11%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>32,11%</t>
+          <t>31,91%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6716,12 +6716,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>578319</t>
+          <t>579058</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>665581</t>
+          <t>661183</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6731,12 +6731,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>29,12%</t>
+          <t>29,15%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>33,51%</t>
+          <t>33,29%</t>
         </is>
       </c>
     </row>
@@ -6759,12 +6759,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>197144</t>
+          <t>199476</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>249564</t>
+          <t>250788</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>20,94%</t>
+          <t>21,19%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>26,51%</t>
+          <t>26,64%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6794,12 +6794,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>154969</t>
+          <t>153249</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>204185</t>
+          <t>205521</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6809,12 +6809,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>14,67%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>19,54%</t>
+          <t>19,67%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6829,12 +6829,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>366220</t>
+          <t>367276</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>441183</t>
+          <t>442380</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6844,12 +6844,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>18,44%</t>
+          <t>18,49%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>22,21%</t>
+          <t>22,27%</t>
         </is>
       </c>
     </row>
@@ -6872,12 +6872,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>104142</t>
+          <t>101945</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>144552</t>
+          <t>144956</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>10,83%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>15,36%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6907,12 +6907,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>77321</t>
+          <t>76152</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>115621</t>
+          <t>113177</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6922,12 +6922,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>10,83%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6942,12 +6942,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>189235</t>
+          <t>191383</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>244523</t>
+          <t>248643</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6957,12 +6957,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>12,31%</t>
+          <t>12,52%</t>
         </is>
       </c>
     </row>
@@ -7102,12 +7102,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>209585</t>
+          <t>213070</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>272252</t>
+          <t>271155</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7137,12 +7137,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>362642</t>
+          <t>362411</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>443178</t>
+          <t>438165</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7152,12 +7152,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>12,4%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>593095</t>
+          <t>590348</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>692354</t>
+          <t>692944</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7187,12 +7187,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>9,98%</t>
         </is>
       </c>
     </row>
@@ -7215,12 +7215,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>647590</t>
+          <t>647472</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>753130</t>
+          <t>749738</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7235,7 +7235,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>22,1%</t>
+          <t>22,0%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7250,12 +7250,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>906844</t>
+          <t>909910</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1018164</t>
+          <t>1016825</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7265,12 +7265,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>25,66%</t>
+          <t>25,74%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>28,81%</t>
+          <t>28,77%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7285,12 +7285,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1581964</t>
+          <t>1585846</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1728320</t>
+          <t>1732648</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7300,12 +7300,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>22,79%</t>
+          <t>22,84%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>24,89%</t>
+          <t>24,96%</t>
         </is>
       </c>
     </row>
@@ -7328,12 +7328,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>977003</t>
+          <t>974775</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>1088173</t>
+          <t>1084349</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7343,12 +7343,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>28,67%</t>
+          <t>28,6%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>31,93%</t>
+          <t>31,82%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7363,12 +7363,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1077312</t>
+          <t>1080192</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>1196618</t>
+          <t>1193293</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7378,12 +7378,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>30,48%</t>
+          <t>30,56%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>33,85%</t>
+          <t>33,76%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7398,12 +7398,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>2093736</t>
+          <t>2083672</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>2254992</t>
+          <t>2247295</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7413,12 +7413,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>30,16%</t>
+          <t>30,01%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>32,48%</t>
+          <t>32,37%</t>
         </is>
       </c>
     </row>
@@ -7441,12 +7441,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>880275</t>
+          <t>880645</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>989122</t>
+          <t>985659</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7456,12 +7456,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>25,83%</t>
+          <t>25,84%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>29,02%</t>
+          <t>28,92%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7476,12 +7476,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>656806</t>
+          <t>654466</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>756770</t>
+          <t>747435</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7491,12 +7491,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>18,52%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>21,41%</t>
+          <t>21,15%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7511,12 +7511,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>1560878</t>
+          <t>1566968</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>1700431</t>
+          <t>1708470</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7526,12 +7526,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>22,48%</t>
+          <t>22,57%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>24,49%</t>
+          <t>24,61%</t>
         </is>
       </c>
     </row>
@@ -7554,12 +7554,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>460807</t>
+          <t>459297</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>545177</t>
+          <t>544713</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7569,12 +7569,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>13,48%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>15,98%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7589,12 +7589,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>306565</t>
+          <t>306449</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>374658</t>
+          <t>377454</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7609,7 +7609,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>10,68%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7624,12 +7624,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>787556</t>
+          <t>786103</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>905659</t>
+          <t>896105</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7639,12 +7639,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>11,32%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>12,91%</t>
         </is>
       </c>
     </row>
@@ -7821,7 +7821,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia de consumo de embutidos y fiambres en 2016</t>
+          <t>Población según la frecuencia de consumo de embutidos y fiambres en 2016 (tasa de respuesta: 99,7%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8016,12 +8016,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>29649</t>
+          <t>29487</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>55063</t>
+          <t>54550</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8051,12 +8051,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>69099</t>
+          <t>69438</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>104073</t>
+          <t>104735</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8066,12 +8066,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>15,59%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8086,12 +8086,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>105641</t>
+          <t>108302</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>150025</t>
+          <t>151335</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8101,12 +8101,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>11,27%</t>
         </is>
       </c>
     </row>
@@ -8129,12 +8129,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>110384</t>
+          <t>108428</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>150643</t>
+          <t>151419</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,46%</t>
+          <t>16,17%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>22,47%</t>
+          <t>22,59%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8164,12 +8164,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>137607</t>
+          <t>134672</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>180658</t>
+          <t>180825</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8179,12 +8179,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>20,48%</t>
+          <t>20,04%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>26,89%</t>
+          <t>26,91%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8199,12 +8199,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>257166</t>
+          <t>261180</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>317920</t>
+          <t>320079</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8214,12 +8214,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>19,16%</t>
+          <t>19,46%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>23,68%</t>
+          <t>23,84%</t>
         </is>
       </c>
     </row>
@@ -8242,12 +8242,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>239077</t>
+          <t>238770</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>288076</t>
+          <t>287944</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8257,12 +8257,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>35,66%</t>
+          <t>35,61%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>42,97%</t>
+          <t>42,95%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8277,12 +8277,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>223055</t>
+          <t>226166</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>273369</t>
+          <t>273761</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8292,12 +8292,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>33,19%</t>
+          <t>33,66%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>40,68%</t>
+          <t>40,74%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8312,12 +8312,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>474467</t>
+          <t>474857</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>546834</t>
+          <t>547338</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8327,12 +8327,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>35,35%</t>
+          <t>35,37%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>40,74%</t>
+          <t>40,77%</t>
         </is>
       </c>
     </row>
@@ -8355,12 +8355,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>146830</t>
+          <t>147664</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>188747</t>
+          <t>194302</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8370,12 +8370,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>21,9%</t>
+          <t>22,03%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>28,15%</t>
+          <t>28,98%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8390,12 +8390,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>123969</t>
+          <t>125709</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>165785</t>
+          <t>165855</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8405,12 +8405,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18,45%</t>
+          <t>18,71%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>24,67%</t>
+          <t>24,68%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8425,12 +8425,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>283969</t>
+          <t>284006</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>344996</t>
+          <t>346520</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8440,12 +8440,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>21,15%</t>
+          <t>21,16%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>25,7%</t>
+          <t>25,81%</t>
         </is>
       </c>
     </row>
@@ -8468,12 +8468,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>54221</t>
+          <t>53559</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>87066</t>
+          <t>84481</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8483,12 +8483,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>12,6%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8503,12 +8503,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>24794</t>
+          <t>24804</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>46775</t>
+          <t>47092</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8523,7 +8523,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8538,12 +8538,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>84380</t>
+          <t>84297</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>123819</t>
+          <t>124969</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8553,12 +8553,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>9,31%</t>
         </is>
       </c>
     </row>
@@ -8698,12 +8698,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>47357</t>
+          <t>47736</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>79157</t>
+          <t>81522</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8713,12 +8713,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8733,12 +8733,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>67580</t>
+          <t>66531</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>102288</t>
+          <t>103916</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8748,12 +8748,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8768,12 +8768,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>122883</t>
+          <t>119834</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>170823</t>
+          <t>168131</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8783,12 +8783,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>8,15%</t>
         </is>
       </c>
     </row>
@@ -8811,12 +8811,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>147616</t>
+          <t>148806</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>199132</t>
+          <t>198779</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8826,12 +8826,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>14,59%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>19,52%</t>
+          <t>19,48%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8846,12 +8846,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>231632</t>
+          <t>231515</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>286499</t>
+          <t>288111</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8861,12 +8861,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>22,23%</t>
+          <t>22,22%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>27,5%</t>
+          <t>27,65%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8881,12 +8881,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>391572</t>
+          <t>391044</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>466225</t>
+          <t>466414</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8896,12 +8896,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>18,99%</t>
+          <t>18,96%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>22,61%</t>
+          <t>22,62%</t>
         </is>
       </c>
     </row>
@@ -8924,12 +8924,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>376887</t>
+          <t>374811</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>439719</t>
+          <t>441097</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8939,12 +8939,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>36,94%</t>
+          <t>36,74%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>43,1%</t>
+          <t>43,23%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8959,12 +8959,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>400298</t>
+          <t>399203</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>462774</t>
+          <t>462324</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8974,12 +8974,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>38,42%</t>
+          <t>38,32%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>44,42%</t>
+          <t>44,37%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8994,12 +8994,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>792315</t>
+          <t>791631</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>887185</t>
+          <t>881955</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9009,12 +9009,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>38,42%</t>
+          <t>38,39%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>43,02%</t>
+          <t>42,77%</t>
         </is>
       </c>
     </row>
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>257487</t>
+          <t>255832</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>317301</t>
+          <t>314909</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9052,12 +9052,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>25,24%</t>
+          <t>25,07%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>31,1%</t>
+          <t>30,87%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9072,12 +9072,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>194962</t>
+          <t>195980</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>247560</t>
+          <t>248670</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9087,12 +9087,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18,71%</t>
+          <t>18,81%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>23,76%</t>
+          <t>23,87%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>465435</t>
+          <t>462944</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>546040</t>
+          <t>545267</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9122,12 +9122,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>22,57%</t>
+          <t>22,45%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>26,48%</t>
+          <t>26,44%</t>
         </is>
       </c>
     </row>
@@ -9150,12 +9150,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>75838</t>
+          <t>74987</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>113819</t>
+          <t>113223</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9165,12 +9165,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9185,12 +9185,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>38180</t>
+          <t>38064</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>66528</t>
+          <t>65729</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9200,12 +9200,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>120952</t>
+          <t>121857</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>169537</t>
+          <t>170406</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9235,12 +9235,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,26%</t>
         </is>
       </c>
     </row>
@@ -9380,12 +9380,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>26859</t>
+          <t>25743</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>53515</t>
+          <t>50504</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9395,12 +9395,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>38155</t>
+          <t>38290</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>66516</t>
+          <t>66547</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9430,7 +9430,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -9450,12 +9450,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>70957</t>
+          <t>71431</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>110172</t>
+          <t>109060</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9465,12 +9465,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,07%</t>
         </is>
       </c>
     </row>
@@ -9493,12 +9493,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>68660</t>
+          <t>69487</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>104986</t>
+          <t>104506</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9508,12 +9508,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>13,77%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9528,12 +9528,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>128341</t>
+          <t>125431</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>174444</t>
+          <t>174331</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9543,12 +9543,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>16,02%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>22,28%</t>
+          <t>22,27%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9563,12 +9563,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>208148</t>
+          <t>209301</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>267806</t>
+          <t>269714</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9578,12 +9578,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>13,58%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>17,5%</t>
         </is>
       </c>
     </row>
@@ -9606,12 +9606,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>278216</t>
+          <t>280252</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>334010</t>
+          <t>336531</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9621,12 +9621,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>36,67%</t>
+          <t>36,94%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>44,02%</t>
+          <t>44,36%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9641,12 +9641,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>252150</t>
+          <t>251876</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>308971</t>
+          <t>310056</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9656,12 +9656,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>32,21%</t>
+          <t>32,17%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>39,46%</t>
+          <t>39,6%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9676,12 +9676,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>547049</t>
+          <t>549396</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>627236</t>
+          <t>625434</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9691,12 +9691,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>35,49%</t>
+          <t>35,64%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>40,69%</t>
+          <t>40,57%</t>
         </is>
       </c>
     </row>
@@ -9719,12 +9719,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>200332</t>
+          <t>198914</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>250237</t>
+          <t>249618</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9734,12 +9734,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>26,41%</t>
+          <t>26,22%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>32,98%</t>
+          <t>32,9%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9754,12 +9754,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>195697</t>
+          <t>194859</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>247089</t>
+          <t>245728</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9769,12 +9769,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>24,89%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>31,56%</t>
+          <t>31,39%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9789,12 +9789,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>406228</t>
+          <t>410322</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>479484</t>
+          <t>477168</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9804,12 +9804,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>26,35%</t>
+          <t>26,62%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>31,1%</t>
+          <t>30,95%</t>
         </is>
       </c>
     </row>
@@ -9832,12 +9832,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>87186</t>
+          <t>85126</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>127885</t>
+          <t>124397</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9847,12 +9847,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>16,86%</t>
+          <t>16,4%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9867,12 +9867,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>64610</t>
+          <t>63593</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>97034</t>
+          <t>97727</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9882,12 +9882,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>12,48%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9902,12 +9902,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>161810</t>
+          <t>159587</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>213569</t>
+          <t>214260</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9917,12 +9917,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>13,85%</t>
+          <t>13,9%</t>
         </is>
       </c>
     </row>
@@ -10062,12 +10062,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>60103</t>
+          <t>59464</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>94689</t>
+          <t>94969</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10077,12 +10077,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10097,12 +10097,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>84685</t>
+          <t>85570</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>126574</t>
+          <t>128491</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10112,12 +10112,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>12,39%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10132,12 +10132,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>154389</t>
+          <t>154834</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>208737</t>
+          <t>209033</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10147,12 +10147,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>10,61%</t>
         </is>
       </c>
     </row>
@@ -10175,12 +10175,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>144557</t>
+          <t>144746</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>191866</t>
+          <t>192840</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10190,12 +10190,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>15,5%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
+          <t>20,66%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10210,12 +10210,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>202797</t>
+          <t>201512</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>257211</t>
+          <t>255308</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10225,12 +10225,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>19,55%</t>
+          <t>19,43%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>24,8%</t>
+          <t>24,61%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10245,12 +10245,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>359293</t>
+          <t>360139</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>430900</t>
+          <t>432329</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10260,12 +10260,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>18,23%</t>
+          <t>18,27%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>21,86%</t>
+          <t>21,94%</t>
         </is>
       </c>
     </row>
@@ -10288,12 +10288,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>302424</t>
+          <t>301446</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>362340</t>
+          <t>358661</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10303,12 +10303,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>32,39%</t>
+          <t>32,29%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>38,81%</t>
+          <t>38,42%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10323,12 +10323,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>346223</t>
+          <t>347074</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>410153</t>
+          <t>408526</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10338,12 +10338,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>33,38%</t>
+          <t>33,46%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>39,54%</t>
+          <t>39,39%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10358,12 +10358,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>659888</t>
+          <t>660620</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>747059</t>
+          <t>747362</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>33,48%</t>
+          <t>33,52%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>37,91%</t>
+          <t>37,92%</t>
         </is>
       </c>
     </row>
@@ -10401,12 +10401,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>220105</t>
+          <t>221344</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>278484</t>
+          <t>273816</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>23,58%</t>
+          <t>23,71%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>29,83%</t>
+          <t>29,33%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10436,12 +10436,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>205103</t>
+          <t>206566</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>261919</t>
+          <t>259290</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10451,12 +10451,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>19,77%</t>
+          <t>19,92%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>25,25%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10471,12 +10471,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>443049</t>
+          <t>444857</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>517030</t>
+          <t>518712</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10486,12 +10486,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>22,48%</t>
+          <t>22,57%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>26,23%</t>
+          <t>26,32%</t>
         </is>
       </c>
     </row>
@@ -10514,12 +10514,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>94772</t>
+          <t>95857</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>135904</t>
+          <t>134379</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10529,12 +10529,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>14,39%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10549,12 +10549,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>78537</t>
+          <t>77581</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>114816</t>
+          <t>114504</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10564,12 +10564,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>11,04%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10584,12 +10584,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>181107</t>
+          <t>183894</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>236932</t>
+          <t>241367</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10599,12 +10599,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>9,33%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>12,25%</t>
         </is>
       </c>
     </row>
@@ -10744,12 +10744,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>185809</t>
+          <t>187745</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>244859</t>
+          <t>245689</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10759,12 +10759,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10779,12 +10779,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>292523</t>
+          <t>289580</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>364346</t>
+          <t>360848</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10794,12 +10794,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10814,12 +10814,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>491731</t>
+          <t>496211</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>585474</t>
+          <t>587343</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10829,12 +10829,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,49%</t>
         </is>
       </c>
     </row>
@@ -10857,12 +10857,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>513489</t>
+          <t>510345</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>597388</t>
+          <t>599091</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10872,12 +10872,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>15,18%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>17,71%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10892,12 +10892,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>746665</t>
+          <t>747812</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>842292</t>
+          <t>848314</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10907,12 +10907,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>21,13%</t>
+          <t>21,16%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>23,83%</t>
+          <t>24,0%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10927,12 +10927,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1280194</t>
+          <t>1276559</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1411400</t>
+          <t>1415379</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10942,12 +10942,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>18,51%</t>
+          <t>18,46%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>20,4%</t>
+          <t>20,46%</t>
         </is>
       </c>
     </row>
@@ -10970,12 +10970,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1248661</t>
+          <t>1248489</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>1368060</t>
+          <t>1366102</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10985,12 +10985,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>36,91%</t>
+          <t>36,9%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>40,44%</t>
+          <t>40,38%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11005,12 +11005,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1274417</t>
+          <t>1278611</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>1392017</t>
+          <t>1396502</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -11020,12 +11020,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>36,06%</t>
+          <t>36,18%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>39,39%</t>
+          <t>39,52%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11040,12 +11040,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>2552526</t>
+          <t>2558240</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>2718940</t>
+          <t>2716770</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11055,12 +11055,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>36,9%</t>
+          <t>36,98%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>39,31%</t>
+          <t>39,28%</t>
         </is>
       </c>
     </row>
@@ -11083,12 +11083,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>878446</t>
+          <t>875819</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>979220</t>
+          <t>981145</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -11098,12 +11098,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>25,97%</t>
+          <t>25,89%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>28,95%</t>
+          <t>29,0%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -11118,12 +11118,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>761784</t>
+          <t>765830</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>870488</t>
+          <t>871166</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -11133,12 +11133,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>21,56%</t>
+          <t>21,67%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>24,63%</t>
+          <t>24,65%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -11153,12 +11153,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>1664328</t>
+          <t>1673183</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>1819276</t>
+          <t>1813779</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -11168,12 +11168,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>24,06%</t>
+          <t>24,19%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>26,3%</t>
+          <t>26,22%</t>
         </is>
       </c>
     </row>
@@ -11196,12 +11196,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>343042</t>
+          <t>342944</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>418599</t>
+          <t>416085</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11216,7 +11216,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>12,3%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11231,12 +11231,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>232074</t>
+          <t>232143</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>293671</t>
+          <t>295231</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -11251,7 +11251,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11266,12 +11266,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>599793</t>
+          <t>599189</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>687842</t>
+          <t>697037</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11281,12 +11281,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>10,08%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P36B10-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P36B10-Habitat-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9805</t>
+          <t>9450</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>27133</t>
+          <t>25928</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>22257</t>
+          <t>22539</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>45714</t>
+          <t>44862</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>36933</t>
+          <t>37429</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>63696</t>
+          <t>65986</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,77%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>46362</t>
+          <t>44530</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>75676</t>
+          <t>72913</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>76462</t>
+          <t>76169</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>111252</t>
+          <t>110979</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>16,12%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>130499</t>
+          <t>131618</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>173711</t>
+          <t>174279</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>12,57%</t>
+          <t>12,61%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>163285</t>
+          <t>162311</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>209733</t>
+          <t>209417</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>23,53%</t>
+          <t>23,39%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>30,22%</t>
+          <t>30,17%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>250085</t>
+          <t>248740</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>300776</t>
+          <t>299816</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>36,33%</t>
+          <t>36,14%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>43,7%</t>
+          <t>43,56%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>431801</t>
+          <t>429309</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>499987</t>
+          <t>497030</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>31,24%</t>
+          <t>31,06%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>36,17%</t>
+          <t>35,96%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>182066</t>
+          <t>180436</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>231474</t>
+          <t>229178</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>26,23%</t>
+          <t>26,0%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>33,35%</t>
+          <t>33,02%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>173731</t>
+          <t>176339</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>221112</t>
+          <t>221978</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>25,24%</t>
+          <t>25,62%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>32,12%</t>
+          <t>32,25%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>370804</t>
+          <t>368333</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>438872</t>
+          <t>435978</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>26,82%</t>
+          <t>26,65%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>31,75%</t>
+          <t>31,54%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>202779</t>
+          <t>203277</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>250599</t>
+          <t>252178</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>29,22%</t>
+          <t>29,29%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>36,11%</t>
+          <t>36,34%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>74153</t>
+          <t>74590</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>109217</t>
+          <t>109188</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>15,86%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>287924</t>
+          <t>290442</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>346540</t>
+          <t>350063</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>20,83%</t>
+          <t>21,01%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>25,07%</t>
+          <t>25,32%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>45052</t>
+          <t>43931</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>76028</t>
+          <t>74569</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>64225</t>
+          <t>62855</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>98010</t>
+          <t>95652</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>113953</t>
+          <t>113040</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>161649</t>
+          <t>159988</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,32%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>80472</t>
+          <t>82068</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>120607</t>
+          <t>120770</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>12,61%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>128606</t>
+          <t>132230</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>176758</t>
+          <t>179119</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>13,71%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>18,32%</t>
+          <t>18,57%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>225366</t>
+          <t>221717</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>288248</t>
+          <t>282796</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>14,71%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>273518</t>
+          <t>269405</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>332614</t>
+          <t>328618</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>28,56%</t>
+          <t>28,13%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>34,73%</t>
+          <t>34,31%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>407791</t>
+          <t>405021</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>471322</t>
+          <t>466610</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>42,27%</t>
+          <t>41,98%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>48,86%</t>
+          <t>48,37%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>691944</t>
+          <t>689536</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>778978</t>
+          <t>778706</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>35,99%</t>
+          <t>35,87%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>40,52%</t>
+          <t>40,51%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>278468</t>
+          <t>280235</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>337647</t>
+          <t>337176</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>29,08%</t>
+          <t>29,26%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>35,26%</t>
+          <t>35,21%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>204595</t>
+          <t>204071</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>257779</t>
+          <t>257612</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>21,21%</t>
+          <t>21,15%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>26,72%</t>
+          <t>26,7%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>500329</t>
+          <t>496474</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>577903</t>
+          <t>576844</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>26,03%</t>
+          <t>25,83%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>30,06%</t>
+          <t>30,01%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>166183</t>
+          <t>165949</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>217141</t>
+          <t>215796</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>17,35%</t>
+          <t>17,33%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>22,67%</t>
+          <t>22,53%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>53914</t>
+          <t>53930</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>85912</t>
+          <t>85913</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>233013</t>
+          <t>233053</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>290825</t>
+          <t>293208</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>15,13%</t>
+          <t>15,25%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>37528</t>
+          <t>39233</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>67730</t>
+          <t>68898</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>77884</t>
+          <t>77775</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>114758</t>
+          <t>113500</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>11,41%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>16,65%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>121536</t>
+          <t>123922</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>169583</t>
+          <t>170376</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>12,54%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>96836</t>
+          <t>93846</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>134666</t>
+          <t>136316</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>14,31%</t>
+          <t>13,87%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>19,9%</t>
+          <t>20,14%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>133028</t>
+          <t>135588</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>176590</t>
+          <t>175923</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>19,51%</t>
+          <t>19,89%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>25,9%</t>
+          <t>25,81%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>240885</t>
+          <t>241235</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>298298</t>
+          <t>299368</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>17,73%</t>
+          <t>17,76%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>21,96%</t>
+          <t>22,04%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>180572</t>
+          <t>180110</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>227334</t>
+          <t>227768</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>26,68%</t>
+          <t>26,61%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>33,59%</t>
+          <t>33,65%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>227420</t>
+          <t>227519</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>277470</t>
+          <t>273723</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>33,36%</t>
+          <t>33,37%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>40,7%</t>
+          <t>40,15%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>418109</t>
+          <t>417170</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>487637</t>
+          <t>486795</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>30,78%</t>
+          <t>30,71%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>35,89%</t>
+          <t>35,83%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>191660</t>
+          <t>190503</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>243074</t>
+          <t>243642</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>28,32%</t>
+          <t>28,15%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>35,92%</t>
+          <t>36,0%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>121434</t>
+          <t>125697</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>164911</t>
+          <t>166175</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>17,81%</t>
+          <t>18,44%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>24,19%</t>
+          <t>24,38%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>330081</t>
+          <t>325489</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>395548</t>
+          <t>393422</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>24,3%</t>
+          <t>23,96%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>29,12%</t>
+          <t>28,96%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>75251</t>
+          <t>73462</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>110195</t>
+          <t>110901</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>10,85%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>16,39%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>28220</t>
+          <t>26815</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>51886</t>
+          <t>51393</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>110796</t>
+          <t>107718</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>153059</t>
+          <t>152891</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>11,25%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>33668</t>
+          <t>34422</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>59591</t>
+          <t>60872</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>56000</t>
+          <t>55625</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>89276</t>
+          <t>88950</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>96874</t>
+          <t>96771</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>139170</t>
+          <t>139227</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>92355</t>
+          <t>91909</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>130731</t>
+          <t>128014</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>13,61%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>152877</t>
+          <t>150272</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>199796</t>
+          <t>201721</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>14,78%</t>
+          <t>14,53%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>19,31%</t>
+          <t>19,5%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>254217</t>
+          <t>252538</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>316697</t>
+          <t>318029</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>12,79%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>16,04%</t>
+          <t>16,1%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>306875</t>
+          <t>306222</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>363227</t>
+          <t>362134</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>32,63%</t>
+          <t>32,56%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>38,62%</t>
+          <t>38,51%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>392447</t>
+          <t>391364</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>456344</t>
+          <t>456327</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,7 +3054,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>37,93%</t>
+          <t>37,83%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>715458</t>
+          <t>717112</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>798943</t>
+          <t>801341</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>36,23%</t>
+          <t>36,31%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>40,45%</t>
+          <t>40,57%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>241894</t>
+          <t>243708</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>298080</t>
+          <t>296133</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>25,72%</t>
+          <t>25,91%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>31,69%</t>
+          <t>31,49%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>212854</t>
+          <t>212376</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>266374</t>
+          <t>268475</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>20,57%</t>
+          <t>20,53%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>25,75%</t>
+          <t>25,95%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>471884</t>
+          <t>468316</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>554130</t>
+          <t>550083</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>23,89%</t>
+          <t>23,71%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>28,06%</t>
+          <t>27,85%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>158836</t>
+          <t>159731</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>205708</t>
+          <t>204471</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>16,89%</t>
+          <t>16,98%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>21,87%</t>
+          <t>21,74%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>106425</t>
+          <t>103922</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>147982</t>
+          <t>145526</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>14,07%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>274613</t>
+          <t>276262</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>341763</t>
+          <t>339414</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>13,99%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>17,3%</t>
+          <t>17,19%</t>
         </is>
       </c>
     </row>
@@ -3460,12 +3460,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>146854</t>
+          <t>146369</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>201403</t>
+          <t>199656</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3475,12 +3475,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>244787</t>
+          <t>244498</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>311349</t>
+          <t>313236</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>411102</t>
+          <t>407309</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>490867</t>
+          <t>491481</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,4%</t>
         </is>
       </c>
     </row>
@@ -3573,12 +3573,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>348305</t>
+          <t>344932</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>421152</t>
+          <t>418158</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3588,12 +3588,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>12,79%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>534591</t>
+          <t>534068</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>618567</t>
+          <t>622481</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>15,85%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>18,36%</t>
+          <t>18,47%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3643,12 +3643,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>898898</t>
+          <t>896196</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1015347</t>
+          <t>1011603</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>15,24%</t>
         </is>
       </c>
     </row>
@@ -3686,12 +3686,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>974825</t>
+          <t>969691</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>1079092</t>
+          <t>1075584</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3701,12 +3701,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>29,82%</t>
+          <t>29,66%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>33,01%</t>
+          <t>32,9%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3721,12 +3721,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1329416</t>
+          <t>1330085</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>1445801</t>
+          <t>1446034</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>39,46%</t>
+          <t>39,48%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>42,91%</t>
+          <t>42,92%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3756,12 +3756,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>2338408</t>
+          <t>2339288</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>2493953</t>
+          <t>2495632</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>35,23%</t>
+          <t>35,24%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>37,57%</t>
+          <t>37,59%</t>
         </is>
       </c>
     </row>
@@ -3799,12 +3799,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>946254</t>
+          <t>947612</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>1051415</t>
+          <t>1058307</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3814,12 +3814,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>28,95%</t>
+          <t>28,99%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>32,16%</t>
+          <t>32,37%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3834,12 +3834,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>760839</t>
+          <t>762498</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>857056</t>
+          <t>857712</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>22,58%</t>
+          <t>22,63%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>25,44%</t>
+          <t>25,46%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3869,12 +3869,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>1731085</t>
+          <t>1733667</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>1879996</t>
+          <t>1879199</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>26,08%</t>
+          <t>26,12%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>28,32%</t>
+          <t>28,31%</t>
         </is>
       </c>
     </row>
@@ -3912,12 +3912,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>644680</t>
+          <t>645820</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>735910</t>
+          <t>740116</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3927,12 +3927,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>19,72%</t>
+          <t>19,76%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>22,51%</t>
+          <t>22,64%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3947,12 +3947,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>290864</t>
+          <t>292854</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>358949</t>
+          <t>359881</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>10,68%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3982,12 +3982,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>959103</t>
+          <t>956040</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1067055</t>
+          <t>1071516</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>14,4%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>16,07%</t>
+          <t>16,14%</t>
         </is>
       </c>
     </row>
@@ -4374,12 +4374,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>30556</t>
+          <t>29267</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>55968</t>
+          <t>55860</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4389,12 +4389,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4409,12 +4409,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>56163</t>
+          <t>58266</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>90495</t>
+          <t>92304</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4424,12 +4424,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>13,4%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>96923</t>
+          <t>92880</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>138695</t>
+          <t>135437</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4459,12 +4459,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>9,75%</t>
         </is>
       </c>
     </row>
@@ -4487,12 +4487,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>130761</t>
+          <t>128230</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>177599</t>
+          <t>173120</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4502,12 +4502,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>18,66%</t>
+          <t>18,3%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>25,35%</t>
+          <t>24,71%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4522,12 +4522,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>152386</t>
+          <t>153576</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>198075</t>
+          <t>199174</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4537,12 +4537,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>22,12%</t>
+          <t>22,29%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>28,75%</t>
+          <t>28,91%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4557,12 +4557,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>295994</t>
+          <t>292803</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>356735</t>
+          <t>356704</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4572,7 +4572,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>21,3%</t>
+          <t>21,07%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -4600,12 +4600,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>193179</t>
+          <t>196550</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>244791</t>
+          <t>244608</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4615,12 +4615,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>27,57%</t>
+          <t>28,06%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>34,94%</t>
+          <t>34,92%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4635,12 +4635,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>238746</t>
+          <t>239089</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>290996</t>
+          <t>289798</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>34,65%</t>
+          <t>34,7%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>42,23%</t>
+          <t>42,06%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4670,12 +4670,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>448189</t>
+          <t>445317</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>523714</t>
+          <t>518700</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>32,25%</t>
+          <t>32,05%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>37,69%</t>
+          <t>37,33%</t>
         </is>
       </c>
     </row>
@@ -4713,12 +4713,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>175599</t>
+          <t>178025</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>225041</t>
+          <t>228837</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4728,12 +4728,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>25,06%</t>
+          <t>25,41%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>32,12%</t>
+          <t>32,66%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>116145</t>
+          <t>114521</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>158806</t>
+          <t>159207</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16,86%</t>
+          <t>16,62%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>23,05%</t>
+          <t>23,11%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>303191</t>
+          <t>308635</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>369120</t>
+          <t>373564</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>21,82%</t>
+          <t>22,21%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>26,56%</t>
+          <t>26,88%</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>72241</t>
+          <t>72479</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>108863</t>
+          <t>107802</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>15,54%</t>
+          <t>15,39%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4861,12 +4861,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>32954</t>
+          <t>32874</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>59079</t>
+          <t>57343</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4896,12 +4896,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>112296</t>
+          <t>109939</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>153874</t>
+          <t>153045</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>11,01%</t>
         </is>
       </c>
     </row>
@@ -5056,12 +5056,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>56688</t>
+          <t>57605</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>92276</t>
+          <t>91937</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5071,12 +5071,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>9,08%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5091,12 +5091,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>78593</t>
+          <t>79816</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>116776</t>
+          <t>119316</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>11,62%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5126,12 +5126,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>146827</t>
+          <t>147401</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>197622</t>
+          <t>199329</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,77%</t>
         </is>
       </c>
     </row>
@@ -5169,12 +5169,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>170026</t>
+          <t>169552</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>221271</t>
+          <t>221313</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5184,7 +5184,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>16,79%</t>
+          <t>16,74%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -5204,12 +5204,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>249705</t>
+          <t>252875</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>309567</t>
+          <t>311577</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>24,32%</t>
+          <t>24,63%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>30,15%</t>
+          <t>30,34%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5239,12 +5239,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>437770</t>
+          <t>435833</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>517017</t>
+          <t>516598</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>21,46%</t>
+          <t>21,37%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>25,35%</t>
+          <t>25,33%</t>
         </is>
       </c>
     </row>
@@ -5282,12 +5282,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>263651</t>
+          <t>260705</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>322386</t>
+          <t>322720</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>26,03%</t>
+          <t>25,74%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>31,83%</t>
+          <t>31,87%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5317,12 +5317,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>290769</t>
+          <t>291860</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>352772</t>
+          <t>355154</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>28,32%</t>
+          <t>28,42%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>34,36%</t>
+          <t>34,59%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>574305</t>
+          <t>570586</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>654628</t>
+          <t>655349</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>28,16%</t>
+          <t>27,98%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>32,1%</t>
+          <t>32,13%</t>
         </is>
       </c>
     </row>
@@ -5395,12 +5395,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>286516</t>
+          <t>284454</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>347336</t>
+          <t>345118</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5410,12 +5410,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>28,29%</t>
+          <t>28,09%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>34,3%</t>
+          <t>34,08%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5430,12 +5430,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>204912</t>
+          <t>205340</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>261861</t>
+          <t>262583</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5445,12 +5445,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19,96%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>25,5%</t>
+          <t>25,57%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5465,12 +5465,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>505909</t>
+          <t>507869</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>587452</t>
+          <t>586433</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>24,8%</t>
+          <t>24,9%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>28,8%</t>
+          <t>28,75%</t>
         </is>
       </c>
     </row>
@@ -5508,12 +5508,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>119207</t>
+          <t>117547</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>164020</t>
+          <t>163446</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5523,12 +5523,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>11,61%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>16,14%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>79262</t>
+          <t>77672</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>116418</t>
+          <t>117377</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5558,12 +5558,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>11,43%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>207369</t>
+          <t>209937</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>265092</t>
+          <t>264900</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5593,12 +5593,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>10,29%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>12,99%</t>
         </is>
       </c>
     </row>
@@ -5738,12 +5738,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>43382</t>
+          <t>44517</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>74814</t>
+          <t>74823</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5753,7 +5753,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -5773,12 +5773,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>67851</t>
+          <t>67745</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>104413</t>
+          <t>107399</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>13,88%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5808,12 +5808,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>120000</t>
+          <t>118479</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>167733</t>
+          <t>168785</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>11,05%</t>
         </is>
       </c>
     </row>
@@ -5851,12 +5851,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>116367</t>
+          <t>118354</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>163571</t>
+          <t>163153</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5866,12 +5866,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>15,45%</t>
+          <t>15,71%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>21,71%</t>
+          <t>21,66%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5886,12 +5886,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>160105</t>
+          <t>157406</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>209043</t>
+          <t>208123</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5901,12 +5901,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>20,69%</t>
+          <t>20,34%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>27,01%</t>
+          <t>26,89%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5921,12 +5921,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>289741</t>
+          <t>290006</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>361988</t>
+          <t>358266</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5936,12 +5936,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>18,97%</t>
+          <t>18,99%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>23,7%</t>
+          <t>23,46%</t>
         </is>
       </c>
     </row>
@@ -5964,12 +5964,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>186264</t>
+          <t>183430</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>238705</t>
+          <t>233411</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5979,12 +5979,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>24,73%</t>
+          <t>24,35%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>31,69%</t>
+          <t>30,98%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>220661</t>
+          <t>219300</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>275188</t>
+          <t>273863</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>28,51%</t>
+          <t>28,34%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>35,56%</t>
+          <t>35,39%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>419683</t>
+          <t>420756</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>494946</t>
+          <t>495171</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>27,48%</t>
+          <t>27,55%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>32,41%</t>
+          <t>32,42%</t>
         </is>
       </c>
     </row>
@@ -6077,12 +6077,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>167815</t>
+          <t>170284</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>216058</t>
+          <t>220520</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6092,12 +6092,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>22,28%</t>
+          <t>22,6%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>28,68%</t>
+          <t>29,27%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>132105</t>
+          <t>131250</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>178451</t>
+          <t>177973</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>17,07%</t>
+          <t>16,96%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>23,06%</t>
+          <t>23,0%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>314083</t>
+          <t>314900</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>381345</t>
+          <t>385195</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>20,57%</t>
+          <t>20,62%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>24,97%</t>
+          <t>25,22%</t>
         </is>
       </c>
     </row>
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>129206</t>
+          <t>128066</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>179364</t>
+          <t>175575</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6205,12 +6205,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>17,15%</t>
+          <t>17,0%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>23,81%</t>
+          <t>23,31%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>87858</t>
+          <t>87523</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>128475</t>
+          <t>129811</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6240,12 +6240,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>11,31%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>16,6%</t>
+          <t>16,77%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>226822</t>
+          <t>225199</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>288211</t>
+          <t>290069</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6275,12 +6275,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>14,85%</t>
+          <t>14,75%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>18,87%</t>
+          <t>18,99%</t>
         </is>
       </c>
     </row>
@@ -6420,12 +6420,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>54232</t>
+          <t>53992</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>85529</t>
+          <t>86527</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6435,12 +6435,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>9,19%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6455,12 +6455,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>120689</t>
+          <t>120888</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>166935</t>
+          <t>165239</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6470,12 +6470,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>11,57%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>15,98%</t>
+          <t>15,82%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6490,12 +6490,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>184804</t>
+          <t>184722</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>242046</t>
+          <t>242026</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6533,12 +6533,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>185353</t>
+          <t>184583</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>239662</t>
+          <t>240667</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6548,12 +6548,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>19,69%</t>
+          <t>19,61%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>25,46%</t>
+          <t>25,57%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6568,12 +6568,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>297334</t>
+          <t>297103</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>358575</t>
+          <t>359993</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>28,46%</t>
+          <t>28,44%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>34,32%</t>
+          <t>34,46%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6603,12 +6603,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>495601</t>
+          <t>499080</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>577962</t>
+          <t>580187</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6618,12 +6618,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>24,95%</t>
+          <t>25,13%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>29,1%</t>
+          <t>29,21%</t>
         </is>
       </c>
     </row>
@@ -6646,12 +6646,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>285282</t>
+          <t>284706</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>346594</t>
+          <t>344536</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6661,12 +6661,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>30,3%</t>
+          <t>30,24%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>36,82%</t>
+          <t>36,6%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6681,12 +6681,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>272818</t>
+          <t>276542</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>333387</t>
+          <t>334988</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6696,12 +6696,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>26,11%</t>
+          <t>26,47%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>31,91%</t>
+          <t>32,06%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6716,12 +6716,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>579058</t>
+          <t>576485</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>661183</t>
+          <t>660418</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6731,12 +6731,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>29,15%</t>
+          <t>29,02%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>33,29%</t>
+          <t>33,25%</t>
         </is>
       </c>
     </row>
@@ -6759,12 +6759,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>199476</t>
+          <t>199502</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>250788</t>
+          <t>252605</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6779,7 +6779,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>26,64%</t>
+          <t>26,83%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6794,12 +6794,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>153249</t>
+          <t>156326</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>205521</t>
+          <t>203521</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6809,12 +6809,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>14,96%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>19,67%</t>
+          <t>19,48%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6829,12 +6829,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>367276</t>
+          <t>365255</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>442380</t>
+          <t>439125</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6844,12 +6844,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>18,49%</t>
+          <t>18,39%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>22,27%</t>
+          <t>22,11%</t>
         </is>
       </c>
     </row>
@@ -6872,12 +6872,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>101945</t>
+          <t>101171</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>144956</t>
+          <t>142039</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6907,12 +6907,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>76152</t>
+          <t>77064</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>113177</t>
+          <t>114636</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6922,12 +6922,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6942,12 +6942,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>191383</t>
+          <t>191019</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>248643</t>
+          <t>247105</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6957,12 +6957,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>12,44%</t>
         </is>
       </c>
     </row>
@@ -7102,12 +7102,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>213070</t>
+          <t>210014</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>271155</t>
+          <t>274493</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7137,12 +7137,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>362411</t>
+          <t>361824</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>438165</t>
+          <t>441530</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7152,12 +7152,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>10,24%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>590348</t>
+          <t>588594</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>692944</t>
+          <t>687901</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7187,12 +7187,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>9,91%</t>
         </is>
       </c>
     </row>
@@ -7215,12 +7215,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>647472</t>
+          <t>653809</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>749738</t>
+          <t>750372</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>19,0%</t>
+          <t>19,18%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>22,0%</t>
+          <t>22,02%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7250,12 +7250,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>909910</t>
+          <t>901738</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1016825</t>
+          <t>1012524</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7265,12 +7265,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>25,74%</t>
+          <t>25,51%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>28,77%</t>
+          <t>28,65%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7285,12 +7285,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1585846</t>
+          <t>1595264</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1732648</t>
+          <t>1741667</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7300,12 +7300,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>22,84%</t>
+          <t>22,98%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>24,96%</t>
+          <t>25,09%</t>
         </is>
       </c>
     </row>
@@ -7328,12 +7328,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>974775</t>
+          <t>983591</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>1084349</t>
+          <t>1089309</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7343,12 +7343,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>28,6%</t>
+          <t>28,86%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>31,82%</t>
+          <t>31,96%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7363,12 +7363,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1080192</t>
+          <t>1081925</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>1193293</t>
+          <t>1198282</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7378,12 +7378,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>30,56%</t>
+          <t>30,61%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>33,76%</t>
+          <t>33,9%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7398,12 +7398,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>2083672</t>
+          <t>2089669</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>2247295</t>
+          <t>2249733</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7413,12 +7413,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>30,01%</t>
+          <t>30,1%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>32,37%</t>
+          <t>32,4%</t>
         </is>
       </c>
     </row>
@@ -7441,12 +7441,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>880645</t>
+          <t>881167</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>985659</t>
+          <t>988572</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7456,12 +7456,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>25,84%</t>
+          <t>25,86%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>28,92%</t>
+          <t>29,01%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7476,12 +7476,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>654466</t>
+          <t>650697</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>747435</t>
+          <t>745635</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7491,12 +7491,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>18,52%</t>
+          <t>18,41%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>21,15%</t>
+          <t>21,1%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7511,12 +7511,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>1566968</t>
+          <t>1558928</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>1708470</t>
+          <t>1711398</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7526,12 +7526,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>22,57%</t>
+          <t>22,45%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>24,61%</t>
+          <t>24,65%</t>
         </is>
       </c>
     </row>
@@ -7554,12 +7554,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>459297</t>
+          <t>455874</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>544713</t>
+          <t>545441</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7569,12 +7569,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>13,48%</t>
+          <t>13,38%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>15,98%</t>
+          <t>16,0%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7589,12 +7589,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>306449</t>
+          <t>306392</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>377454</t>
+          <t>378004</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7609,7 +7609,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>10,69%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7624,12 +7624,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>786103</t>
+          <t>786043</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>896105</t>
+          <t>894113</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7644,7 +7644,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>12,88%</t>
         </is>
       </c>
     </row>
@@ -8016,12 +8016,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>29487</t>
+          <t>30087</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>54550</t>
+          <t>54529</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8051,12 +8051,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>69438</t>
+          <t>70415</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>104735</t>
+          <t>103590</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8066,12 +8066,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>10,48%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,59%</t>
+          <t>15,42%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8086,12 +8086,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>108302</t>
+          <t>105649</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>151335</t>
+          <t>149990</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8101,12 +8101,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>11,17%</t>
         </is>
       </c>
     </row>
@@ -8129,12 +8129,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>108428</t>
+          <t>108911</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>151419</t>
+          <t>149969</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,17%</t>
+          <t>16,25%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>22,59%</t>
+          <t>22,37%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8164,12 +8164,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>134672</t>
+          <t>139455</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>180825</t>
+          <t>181764</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8179,12 +8179,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>20,04%</t>
+          <t>20,75%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>26,91%</t>
+          <t>27,05%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8199,12 +8199,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>261180</t>
+          <t>259521</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>320079</t>
+          <t>318653</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8214,12 +8214,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>19,46%</t>
+          <t>19,33%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>23,84%</t>
+          <t>23,74%</t>
         </is>
       </c>
     </row>
@@ -8242,12 +8242,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>238770</t>
+          <t>237424</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>287944</t>
+          <t>288102</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8257,12 +8257,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>35,61%</t>
+          <t>35,41%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>42,95%</t>
+          <t>42,97%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8277,12 +8277,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>226166</t>
+          <t>224089</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>273761</t>
+          <t>276013</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8292,12 +8292,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>33,66%</t>
+          <t>33,35%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>40,74%</t>
+          <t>41,08%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8312,12 +8312,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>474857</t>
+          <t>476438</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>547338</t>
+          <t>548201</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8327,12 +8327,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>35,37%</t>
+          <t>35,49%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>40,77%</t>
+          <t>40,84%</t>
         </is>
       </c>
     </row>
@@ -8355,12 +8355,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>147664</t>
+          <t>145248</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>194302</t>
+          <t>193140</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8370,12 +8370,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>22,03%</t>
+          <t>21,67%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>28,98%</t>
+          <t>28,81%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8390,12 +8390,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>125709</t>
+          <t>123745</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>165855</t>
+          <t>165573</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8405,12 +8405,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18,71%</t>
+          <t>18,42%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>24,68%</t>
+          <t>24,64%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8425,12 +8425,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>284006</t>
+          <t>283195</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>346520</t>
+          <t>345498</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8440,12 +8440,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>21,16%</t>
+          <t>21,1%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>25,81%</t>
+          <t>25,74%</t>
         </is>
       </c>
     </row>
@@ -8468,12 +8468,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>53559</t>
+          <t>52987</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>84481</t>
+          <t>84451</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8483,7 +8483,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -8503,12 +8503,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>24804</t>
+          <t>24823</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>47092</t>
+          <t>47106</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8538,12 +8538,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>84297</t>
+          <t>84007</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>124969</t>
+          <t>122784</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8553,12 +8553,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,15%</t>
         </is>
       </c>
     </row>
@@ -8698,12 +8698,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>47736</t>
+          <t>47983</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>81522</t>
+          <t>79337</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8713,12 +8713,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8733,12 +8733,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>66531</t>
+          <t>64788</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>103916</t>
+          <t>100806</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8748,12 +8748,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8768,12 +8768,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>119834</t>
+          <t>124444</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>168131</t>
+          <t>172834</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8783,12 +8783,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>8,38%</t>
         </is>
       </c>
     </row>
@@ -8811,12 +8811,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>148806</t>
+          <t>149960</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>198779</t>
+          <t>197555</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8826,12 +8826,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>14,7%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>19,48%</t>
+          <t>19,36%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8846,12 +8846,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>231515</t>
+          <t>230240</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>288111</t>
+          <t>289924</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8861,12 +8861,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>22,22%</t>
+          <t>22,1%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>27,65%</t>
+          <t>27,83%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8881,12 +8881,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>391044</t>
+          <t>394875</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>466414</t>
+          <t>471391</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8896,12 +8896,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>18,96%</t>
+          <t>19,15%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>22,62%</t>
+          <t>22,86%</t>
         </is>
       </c>
     </row>
@@ -8924,12 +8924,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>374811</t>
+          <t>376186</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>441097</t>
+          <t>440315</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8939,12 +8939,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>36,74%</t>
+          <t>36,87%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>43,23%</t>
+          <t>43,16%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8959,12 +8959,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>399203</t>
+          <t>398377</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>462324</t>
+          <t>461366</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8974,12 +8974,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>38,32%</t>
+          <t>38,24%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>44,37%</t>
+          <t>44,28%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8994,12 +8994,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>791631</t>
+          <t>792890</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>881955</t>
+          <t>883057</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9009,12 +9009,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>38,39%</t>
+          <t>38,45%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>42,77%</t>
+          <t>42,82%</t>
         </is>
       </c>
     </row>
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>255832</t>
+          <t>259271</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>314909</t>
+          <t>318338</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9052,12 +9052,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>25,07%</t>
+          <t>25,41%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>30,87%</t>
+          <t>31,2%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9072,12 +9072,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>195980</t>
+          <t>195873</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>248670</t>
+          <t>249417</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9087,12 +9087,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18,81%</t>
+          <t>18,8%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>23,87%</t>
+          <t>23,94%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>462944</t>
+          <t>468510</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>545267</t>
+          <t>550813</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9122,12 +9122,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>22,45%</t>
+          <t>22,72%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>26,44%</t>
+          <t>26,71%</t>
         </is>
       </c>
     </row>
@@ -9150,12 +9150,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>74987</t>
+          <t>77192</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>113223</t>
+          <t>113208</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9165,7 +9165,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -9185,12 +9185,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>38064</t>
+          <t>38145</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>65729</t>
+          <t>66388</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9200,12 +9200,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>121857</t>
+          <t>121360</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>170406</t>
+          <t>169834</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9235,12 +9235,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,24%</t>
         </is>
       </c>
     </row>
@@ -9380,12 +9380,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>25743</t>
+          <t>25835</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>50504</t>
+          <t>52041</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9395,12 +9395,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>38290</t>
+          <t>38592</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>66547</t>
+          <t>66725</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9430,12 +9430,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9450,12 +9450,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>71431</t>
+          <t>72483</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>109060</t>
+          <t>113334</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9465,12 +9465,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>7,35%</t>
         </is>
       </c>
     </row>
@@ -9493,12 +9493,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>69487</t>
+          <t>68964</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>104506</t>
+          <t>104364</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9508,12 +9508,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>13,77%</t>
+          <t>13,76%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9528,12 +9528,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>125431</t>
+          <t>129851</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>174331</t>
+          <t>172984</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9543,12 +9543,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>16,02%</t>
+          <t>16,59%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>22,27%</t>
+          <t>22,09%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9563,12 +9563,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>209301</t>
+          <t>208588</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>269714</t>
+          <t>265734</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9578,12 +9578,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>13,53%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>17,5%</t>
+          <t>17,24%</t>
         </is>
       </c>
     </row>
@@ -9606,12 +9606,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>280252</t>
+          <t>278694</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>336531</t>
+          <t>333382</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9621,12 +9621,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>36,94%</t>
+          <t>36,73%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>44,36%</t>
+          <t>43,94%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9641,12 +9641,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>251876</t>
+          <t>251949</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>310056</t>
+          <t>308654</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9656,12 +9656,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>32,17%</t>
+          <t>32,18%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>39,6%</t>
+          <t>39,42%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9676,12 +9676,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>549396</t>
+          <t>544662</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>625434</t>
+          <t>625696</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9691,12 +9691,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>35,64%</t>
+          <t>35,33%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>40,57%</t>
+          <t>40,59%</t>
         </is>
       </c>
     </row>
@@ -9719,12 +9719,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>198914</t>
+          <t>197611</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>249618</t>
+          <t>250711</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9734,12 +9734,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>26,22%</t>
+          <t>26,05%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>32,9%</t>
+          <t>33,05%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9754,12 +9754,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>194859</t>
+          <t>194323</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>245728</t>
+          <t>245102</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9769,12 +9769,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>24,89%</t>
+          <t>24,82%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>31,39%</t>
+          <t>31,31%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9789,12 +9789,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>410322</t>
+          <t>408309</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>477168</t>
+          <t>481173</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9804,12 +9804,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>26,62%</t>
+          <t>26,49%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>30,95%</t>
+          <t>31,21%</t>
         </is>
       </c>
     </row>
@@ -9832,12 +9832,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>85126</t>
+          <t>87224</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>124397</t>
+          <t>127453</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9847,12 +9847,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>16,8%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9867,12 +9867,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>63593</t>
+          <t>64889</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>97727</t>
+          <t>97981</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9882,12 +9882,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>12,51%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9902,12 +9902,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>159587</t>
+          <t>160671</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>214260</t>
+          <t>213080</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9917,12 +9917,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>13,82%</t>
         </is>
       </c>
     </row>
@@ -10062,12 +10062,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>59464</t>
+          <t>61375</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>94969</t>
+          <t>95376</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10077,12 +10077,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10097,12 +10097,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>85570</t>
+          <t>85971</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>128491</t>
+          <t>126137</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10112,12 +10112,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>12,16%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10132,12 +10132,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>154834</t>
+          <t>153580</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>209033</t>
+          <t>208227</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10147,12 +10147,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>10,57%</t>
         </is>
       </c>
     </row>
@@ -10175,12 +10175,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>144746</t>
+          <t>145973</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>192840</t>
+          <t>189874</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10190,12 +10190,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>15,64%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>20,66%</t>
+          <t>20,34%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10210,12 +10210,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>201512</t>
+          <t>200741</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>255308</t>
+          <t>255482</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10225,12 +10225,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>19,43%</t>
+          <t>19,35%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>24,61%</t>
+          <t>24,63%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10245,12 +10245,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>360139</t>
+          <t>358883</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>432329</t>
+          <t>430778</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10260,12 +10260,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>18,27%</t>
+          <t>18,21%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>21,94%</t>
+          <t>21,86%</t>
         </is>
       </c>
     </row>
@@ -10288,12 +10288,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>301446</t>
+          <t>297671</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>358661</t>
+          <t>355111</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10303,12 +10303,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>32,29%</t>
+          <t>31,88%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>38,42%</t>
+          <t>38,04%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10323,12 +10323,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>347074</t>
+          <t>346858</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>408526</t>
+          <t>407316</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10338,12 +10338,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>33,46%</t>
+          <t>33,44%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>39,39%</t>
+          <t>39,27%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10358,12 +10358,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>660620</t>
+          <t>661709</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>747362</t>
+          <t>746765</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>33,52%</t>
+          <t>33,57%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>37,92%</t>
+          <t>37,89%</t>
         </is>
       </c>
     </row>
@@ -10401,12 +10401,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>221344</t>
+          <t>224048</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>273816</t>
+          <t>275918</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>23,71%</t>
+          <t>24,0%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>29,33%</t>
+          <t>29,55%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10436,12 +10436,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>206566</t>
+          <t>206159</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>259290</t>
+          <t>261152</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10451,12 +10451,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>19,92%</t>
+          <t>19,88%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>25,18%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10471,12 +10471,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>444857</t>
+          <t>444914</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>518712</t>
+          <t>519260</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10491,7 +10491,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>26,32%</t>
+          <t>26,35%</t>
         </is>
       </c>
     </row>
@@ -10514,12 +10514,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>95857</t>
+          <t>92531</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>134379</t>
+          <t>133186</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10529,12 +10529,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>14,39%</t>
+          <t>14,27%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10549,12 +10549,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>77581</t>
+          <t>76860</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>114504</t>
+          <t>114497</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10564,7 +10564,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -10584,12 +10584,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>183894</t>
+          <t>182734</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>241367</t>
+          <t>237192</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10599,12 +10599,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>12,04%</t>
         </is>
       </c>
     </row>
@@ -10744,12 +10744,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>187745</t>
+          <t>189407</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>245689</t>
+          <t>245582</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10759,7 +10759,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -10779,12 +10779,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>289580</t>
+          <t>291734</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>360848</t>
+          <t>360366</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10794,12 +10794,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10814,12 +10814,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>496211</t>
+          <t>497151</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>587343</t>
+          <t>589451</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10829,12 +10829,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,52%</t>
         </is>
       </c>
     </row>
@@ -10857,12 +10857,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>510345</t>
+          <t>509138</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>599091</t>
+          <t>596848</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10872,12 +10872,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>15,09%</t>
+          <t>15,05%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>17,71%</t>
+          <t>17,64%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10892,12 +10892,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>747812</t>
+          <t>737806</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>848314</t>
+          <t>841440</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10907,12 +10907,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>21,16%</t>
+          <t>20,88%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>24,0%</t>
+          <t>23,81%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10927,12 +10927,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1276559</t>
+          <t>1277045</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1415379</t>
+          <t>1413414</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10947,7 +10947,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>20,46%</t>
+          <t>20,43%</t>
         </is>
       </c>
     </row>
@@ -10970,12 +10970,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1248489</t>
+          <t>1252100</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>1366102</t>
+          <t>1364568</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10985,12 +10985,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>36,9%</t>
+          <t>37,01%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>40,38%</t>
+          <t>40,34%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11005,12 +11005,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1278611</t>
+          <t>1278991</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>1396502</t>
+          <t>1392544</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -11020,12 +11020,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>36,18%</t>
+          <t>36,19%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>39,52%</t>
+          <t>39,4%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11040,12 +11040,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>2558240</t>
+          <t>2566484</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>2716770</t>
+          <t>2725484</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11055,12 +11055,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>36,98%</t>
+          <t>37,1%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>39,28%</t>
+          <t>39,4%</t>
         </is>
       </c>
     </row>
@@ -11083,12 +11083,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>875819</t>
+          <t>872904</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>981145</t>
+          <t>982640</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -11098,12 +11098,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>25,89%</t>
+          <t>25,8%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>29,0%</t>
+          <t>29,05%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -11118,12 +11118,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>765830</t>
+          <t>765336</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>871166</t>
+          <t>867257</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -11133,12 +11133,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>21,67%</t>
+          <t>21,66%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>24,65%</t>
+          <t>24,54%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -11153,12 +11153,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>1673183</t>
+          <t>1669102</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>1813779</t>
+          <t>1816028</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -11168,12 +11168,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>24,19%</t>
+          <t>24,13%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>26,22%</t>
+          <t>26,25%</t>
         </is>
       </c>
     </row>
@@ -11196,12 +11196,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>342944</t>
+          <t>343499</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>416085</t>
+          <t>420839</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11211,12 +11211,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>10,15%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>12,44%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11231,12 +11231,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>232143</t>
+          <t>233141</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>295231</t>
+          <t>294764</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -11246,12 +11246,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11266,12 +11266,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>599189</t>
+          <t>593912</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>697037</t>
+          <t>695860</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11281,12 +11281,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>10,06%</t>
         </is>
       </c>
     </row>
